--- a/1_sinif/bahar/Kimyasal_Maddeler_ve_Tehlikeleri_Soru_Bankasi.xlsx
+++ b/1_sinif/bahar/Kimyasal_Maddeler_ve_Tehlikeleri_Soru_Bankasi.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,56 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001B5E3A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00065F46"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A5800"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009A3412"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00444444"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -82,48 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -625,7 +549,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Maddenin kolay üremi bulunabilme, yani uyumlu ya da uyumsuz olma özellikleri; • Tehlike sını (parlayıcı, toksik, oksitleyici vb.), • pH değeri (asidik, bazik vb.), • Genel kimyasal yapısı (organik ya da inorganik), • Maddenin hâli (ka, sıvı ve gaz)</t>
+          <t>Maddenin kolay üremi</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,7 +774,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Depolama kodları (GHS) sisteminde eski AB sınıflandırma sisteminde geçen R- ibarelerinin (Risk Phrases) yerini Tehlike Cümleleri/Zarar ifadeleri (H-İfadeleri/H-İbareleri: Hazard Statements) ve S- ibarelerinin (Safety Phrases) yerini Önlem Cümleleri/Önlem İfadeleri (P-İfadeleri/P-İbareleri: Precauonary Statements) almışr. Zarar İfadeleri: H • H200 Serisi: Fiziksel zarar ifadeleri ve kodları • H300 Serisi: Sağlığa ilişkin zarar ifadeleri ve kodları • H400 Serisi: Çevresel zarar ifadeleri ve kodları • İlave zarar ifadeleri ve kodları • Fiziksel özellikler • Sağlığa ilişkin özellikler • Bazı karışımlara ilişkin ilave eket unsurları/bilgileri CEVAP AN</t>
+          <t>Depolama kodları</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -975,7 +899,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Depolama maliye</t>
+          <t>Depolama maliyeti</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1075,7 +999,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Gaz tüplerinin eketlenmesi önlenmesi mümkün değil ise, patlama için azami konsantrasyonunun oluşmasının engellenmesi gerekir. Gazlar ve tozlar havada belli konsantrasyona erişklerinde patlama riski oluştururlar. Eğer oksijen konsantrasyonu veya gaz konsantrasyonu güvenilir sınırlarda tutulabilirse, patlama tehlikesi engellenmiş olur.</t>
+          <t>Gaz tüplerinin eketlenmesi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1165,7 +1089,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Türkiye Atom Enerjisi Kurumu yönetmeliklere göre, TAEK’den izin alınmadan radyasyon üreten tesis ve cihazlar herhangi bir amaç için bulundurulamaz, kurulamaz ve kullanılamaz. Ancak TAEK ulusal bir kurumdur. Uluslararası kurumlar arasında yer almaz. NAHTARI</t>
+          <t>Türkiye Atom Enerjisi Kurumu</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1210,7 +1134,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fenbütadin oksit KİRLETİCİLERİ UN3077'dir. 8. ünitenin 6. ve 7. sayfalarındadır cevabı.</t>
+          <t>Fenbütadin oksit</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1290,7 +1214,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yanıcı özelliğe sahip maddelerle çalışıldıktan sonra, ilgili maddeler hemen çalışma ortamından uzaklaşrılmalıdır.</t>
+          <t>Yanıcı özelliğe sahip maddelerle çalışıldıktan sonra, ilgili</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1300,7 +1224,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Alevle çalışılacak ortamın yakınlarında kolay alev alabilen maddeler bulundurulmamalıdır. sorularından 10. sorudur.</t>
+          <t>Alevle çalışılacak ortamın yakınlarında kolay alev alabilen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,7 +1539,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Uyarı kelimesi, ürünün potansiyel bir tehlikesi konusunda uyarıda bulunmak için tehlikenin göreli ciddiyet seviyesini belirr. güvenli kullanım yollarını ve ürüne kaza sonucu maruz kaldığınız takdirde ne tür tedbirler almanız gerekğini açıklar.</t>
+          <t>Uyarı kelimesi, ürünün potansiyel bir tehlikesi konusunda</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2245,7 +2169,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Azotdioksit: Aşırı toksin gazlar olmayan, Düşük toksinli Gazlar Helyum, Kripton, Neon, Azot, Nitroz oksit. Oksijen, Sülfür hekzaflorür, Ksenon Yani azot gazı yanıcı değildir.</t>
+          <t>Azotdioksit: Aşırı toksin gazlar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2290,7 +2214,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Butanon ppm ile diğerlerinden en yüksekr.</t>
+          <t>Butanon</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3225,7 +3149,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Taşıma görevlisi tehlikeli maddenin risklerine göre kişisel koruyucu donanım (KKD) giymelidir.</t>
+          <t>Taşıma görevlisi tehlikeli maddenin riskleri hakkında</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3280,7 +3204,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tehlikeli maddeler kucakta, elde değil; tekerlekli ve kenarları destekli yük taşıma arabaları veya kapları ile taşınmalıdır.</t>
+          <t>Tehlikeli maddeler kucakta, elde değil; tekerlekli ve kenarları</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4855,7 +4779,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Zehirlenmeye sebep olan madde tahriş edici bir türden ise kişiye kusturma işlemi uygulanmaz.</t>
+          <t>Zehirlenmeye sebep olan madde tahriş edici bir türden ise</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4945,7 +4869,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tehlike (H) ifadeleri, tehlikeli bir ürünün tehlikesinin doğasını açıklar, buna uygun olan yerlerde tehlikenin derecesi de dâhildir.</t>
+          <t>Tehlike (H) ifadeleri, tehlikeli bir ürünün tehlikesinin doğasını</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5215,7 +5139,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Depolanması için özel kaplar kullanılır. kaynama buharı insan dokusunu hızlı bir şekilde dondurur.</t>
+          <t>Depolanması için özel kaplar kullanılır.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5395,7 +5319,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Patlayıcı maddeler yasal olarak karanlık alanlarda tutulmalıdır. alanlarda tutulma zorunluluğu yoktur.</t>
+          <t>Patlayıcı maddeler yasal olarak karanlık alanlarda</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5620,7 +5544,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sağlığa etkileri konusunda, sınırlı bilimsel veri bulunan maddeler referans süre için ölçülen veya hesaplanan zaman ağırlıklı ortalama.</t>
+          <t>Sağlığa etkileri konusunda, sınırlı bilimsel veri bulunan</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">

--- a/1_sinif/bahar/Kimyasal_Maddeler_ve_Tehlikeleri_Soru_Bankasi.xlsx
+++ b/1_sinif/bahar/Kimyasal_Maddeler_ve_Tehlikeleri_Soru_Bankasi.xlsx
@@ -512,6 +512,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -557,6 +558,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -602,6 +604,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -647,6 +650,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -692,6 +696,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -737,6 +742,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -782,6 +788,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -827,6 +834,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -872,6 +880,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -917,6 +926,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -962,6 +972,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1007,6 +1018,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1052,6 +1064,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1097,6 +1110,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1142,6 +1156,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1187,6 +1202,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1232,6 +1248,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1277,6 +1294,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1322,6 +1340,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1359,7 +1378,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kresol NAHTARI</t>
+          <t>Kresol</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1367,6 +1386,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1412,6 +1432,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1457,6 +1478,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1502,6 +1524,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1547,6 +1570,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1584,7 +1608,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>150 mg/kg NAHTARI</t>
+          <t>150 mg/kg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1592,6 +1616,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1637,6 +1662,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1682,6 +1708,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1727,6 +1754,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1772,6 +1800,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1817,6 +1846,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1862,6 +1892,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1907,6 +1938,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1944,7 +1976,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Soğurulma dozu-Gray CEVAP AN</t>
+          <t>Soğurulma dozu-Gray</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1952,6 +1984,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1997,6 +2030,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2042,6 +2076,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2087,6 +2122,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2132,6 +2168,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2177,6 +2214,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2222,6 +2260,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2267,6 +2306,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2304,7 +2344,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tam akusk baret CEVAP AN</t>
+          <t>Tam akusk baret</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2312,6 +2352,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2357,6 +2398,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2394,7 +2436,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tozluk CEVAP AN</t>
+          <t>Tozluk</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2402,6 +2444,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2447,6 +2490,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2492,6 +2536,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2537,6 +2582,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2582,6 +2628,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2627,6 +2674,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2672,6 +2720,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2717,6 +2766,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2762,6 +2812,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2807,6 +2858,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2844,7 +2896,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kimyasalların etkin yönemini sağlamak NAHTARI</t>
+          <t>Kimyasalların etkin yönemini sağlamak</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2852,6 +2904,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2897,6 +2950,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2942,6 +2996,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2987,6 +3042,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3032,6 +3088,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3069,7 +3126,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Üst beden CEVAP AN</t>
+          <t>Üst beden</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3077,6 +3134,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3122,6 +3180,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3167,6 +3226,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3212,6 +3272,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3249,7 +3310,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Eleme veya ikame NAHTARI</t>
+          <t>Eleme veya ikame</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3257,6 +3318,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3302,6 +3364,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3347,6 +3410,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3392,6 +3456,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3437,6 +3502,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3482,6 +3548,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3527,6 +3594,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3572,6 +3640,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3617,6 +3686,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3662,6 +3732,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3707,6 +3778,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3744,7 +3816,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Dikkat NAHTARI</t>
+          <t>Dikkat</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3752,6 +3824,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3797,6 +3870,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3842,6 +3916,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3887,6 +3962,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3932,6 +4008,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3977,6 +4054,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4022,6 +4100,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4067,6 +4146,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4112,6 +4192,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4157,6 +4238,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4202,6 +4284,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4247,6 +4330,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4292,6 +4376,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4337,6 +4422,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4382,6 +4468,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4427,6 +4514,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4472,6 +4560,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4517,6 +4606,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4554,7 +4644,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>I, II, III ve IV CEVAP AN</t>
+          <t>I, II, III ve IV</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4562,6 +4652,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4607,6 +4698,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4652,6 +4744,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4697,6 +4790,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4742,6 +4836,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4787,6 +4882,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4832,6 +4928,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4877,6 +4974,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4922,6 +5020,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4967,6 +5066,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5012,6 +5112,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5057,6 +5158,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5102,6 +5204,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5147,6 +5250,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5184,7 +5288,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>P500 NAHTARI</t>
+          <t>P500</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5192,6 +5296,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5237,6 +5342,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5282,6 +5388,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5327,6 +5434,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5372,6 +5480,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5417,6 +5526,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5462,6 +5572,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5507,6 +5618,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5552,6 +5664,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5597,6 +5710,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5642,6 +5756,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5687,6 +5802,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5732,6 +5848,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5777,6 +5894,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5814,7 +5932,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kulak CEVAP AN</t>
+          <t>Kulak</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5822,6 +5940,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5867,6 +5986,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5912,6 +6032,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5957,6 +6078,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6002,6 +6124,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6047,6 +6170,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
